--- a/diseases/d100/2000-2004.xlsx
+++ b/diseases/d100/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -1539,9 +1536,6 @@
       <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.1781393214272433</v>
       </c>
@@ -2083,9 +2077,6 @@
       <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -2479,9 +2470,6 @@
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -3023,9 +3011,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3419,9 +3404,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.02226741517840542</v>
       </c>
@@ -3963,9 +3945,6 @@
       <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -4359,9 +4338,6 @@
       <c r="O21" t="n">
         <v>4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -4903,9 +4879,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -5299,9 +5272,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04453483035681084</v>
       </c>
@@ -5843,9 +5813,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -6239,9 +6206,6 @@
       <c r="O31" t="n">
         <v>5</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -6783,9 +6747,6 @@
       <c r="O34" t="n">
         <v>6</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -7179,9 +7140,6 @@
       <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1113370758920271</v>
       </c>
@@ -7723,9 +7681,6 @@
       <c r="O39" t="n">
         <v>6</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -8119,9 +8074,6 @@
       <c r="O41" t="n">
         <v>6</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -8663,9 +8615,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -9059,9 +9008,6 @@
       <c r="O46" t="n">
         <v>4</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -9603,9 +9549,6 @@
       <c r="O49" t="n">
         <v>5</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -9999,9 +9942,6 @@
       <c r="O51" t="n">
         <v>4</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -10543,9 +10483,6 @@
       <c r="O54" t="n">
         <v>4</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -10939,9 +10876,6 @@
       <c r="O56" t="n">
         <v>4</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -11483,9 +11417,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11879,9 +11810,6 @@
       <c r="O61" t="n">
         <v>9</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -12423,9 +12351,6 @@
       <c r="O64" t="n">
         <v>3</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -13049,9 +12974,6 @@
       <c r="O67" t="n">
         <v>5</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1107749215325843</v>
       </c>
@@ -13593,9 +13515,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -13989,9 +13908,6 @@
       <c r="O72" t="n">
         <v>6</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -14533,9 +14449,6 @@
       <c r="O75" t="n">
         <v>5</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -14929,9 +14842,6 @@
       <c r="O77" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -15473,9 +15383,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -15869,9 +15776,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -16413,9 +16317,6 @@
       <c r="O85" t="n">
         <v>7</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -16809,9 +16710,6 @@
       <c r="O87" t="n">
         <v>2</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.04430996861303373</v>
       </c>
@@ -17353,9 +17251,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -17749,9 +17644,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -18293,9 +18185,6 @@
       <c r="O95" t="n">
         <v>4</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -18689,9 +18578,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.02215498430651687</v>
       </c>
@@ -19233,9 +19119,6 @@
       <c r="O100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -19629,9 +19512,6 @@
       <c r="O102" t="n">
         <v>3</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -20173,9 +20053,6 @@
       <c r="O105" t="n">
         <v>6</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -20569,9 +20446,6 @@
       <c r="O107" t="n">
         <v>4</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -21113,9 +20987,6 @@
       <c r="O110" t="n">
         <v>7</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -21509,9 +21380,6 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.08861993722606747</v>
       </c>
@@ -22053,9 +21921,6 @@
       <c r="O115" t="n">
         <v>7</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -22449,9 +22314,6 @@
       <c r="O117" t="n">
         <v>6</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.1329299058391012</v>
       </c>
@@ -22993,9 +22855,6 @@
       <c r="O120" t="n">
         <v>5</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -23389,9 +23248,6 @@
       <c r="O122" t="n">
         <v>12</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -23933,9 +23789,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -24559,9 +24412,6 @@
       <c r="O128" t="n">
         <v>6</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -25103,9 +24953,6 @@
       <c r="O131" t="n">
         <v>5</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -25499,9 +25346,6 @@
       <c r="O133" t="n">
         <v>4</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -26043,9 +25887,6 @@
       <c r="O136" t="n">
         <v>3</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -26439,9 +26280,6 @@
       <c r="O138" t="n">
         <v>7</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -26983,9 +26821,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -27379,9 +27214,6 @@
       <c r="O143" t="n">
         <v>5</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -27923,9 +27755,6 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -28319,9 +28148,6 @@
       <c r="O148" t="n">
         <v>7</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -28863,9 +28689,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -29259,9 +29082,6 @@
       <c r="O153" t="n">
         <v>7</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -29803,9 +29623,6 @@
       <c r="O156" t="n">
         <v>2</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -30199,9 +30016,6 @@
       <c r="O158" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0661082138574275</v>
       </c>
@@ -30743,9 +30557,6 @@
       <c r="O161" t="n">
         <v>2</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -31139,9 +30950,6 @@
       <c r="O163" t="n">
         <v>4</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -31683,9 +31491,6 @@
       <c r="O166" t="n">
         <v>3</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -32079,9 +31884,6 @@
       <c r="O168" t="n">
         <v>5</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -32623,9 +32425,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -33019,9 +32818,6 @@
       <c r="O173" t="n">
         <v>4</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -33563,9 +33359,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -33959,9 +33752,6 @@
       <c r="O178" t="n">
         <v>9</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -34503,9 +34293,6 @@
       <c r="O181" t="n">
         <v>5</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -34899,9 +34686,6 @@
       <c r="O183" t="n">
         <v>8</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -35443,9 +35227,6 @@
       <c r="O186" t="n">
         <v>5</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -36069,9 +35850,6 @@
       <c r="O189" t="n">
         <v>13</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -36761,9 +36539,6 @@
       <c r="O193" t="n">
         <v>2</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -37157,9 +36932,6 @@
       <c r="O195" t="n">
         <v>8</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.1752591480346111</v>
       </c>
@@ -37849,9 +37621,6 @@
       <c r="O199" t="n">
         <v>4</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -38245,9 +38014,6 @@
       <c r="O201" t="n">
         <v>2</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -38937,9 +38703,6 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -39333,9 +39096,6 @@
       <c r="O207" t="n">
         <v>6</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -40025,9 +39785,6 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -40421,9 +40178,6 @@
       <c r="O213" t="n">
         <v>6</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -40965,9 +40719,6 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -41361,9 +41112,6 @@
       <c r="O218" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.04381478700865277</v>
       </c>
@@ -42053,9 +41801,6 @@
       <c r="O222" t="n">
         <v>2</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -42449,9 +42194,6 @@
       <c r="O224" t="n">
         <v>4</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -42993,9 +42735,6 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -43389,9 +43128,6 @@
       <c r="O229" t="n">
         <v>5</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.1095369675216319</v>
       </c>
@@ -44081,9 +43817,6 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -44477,9 +44210,6 @@
       <c r="O235" t="n">
         <v>4</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.08762957401730553</v>
       </c>
@@ -45021,9 +44751,6 @@
       <c r="O238" t="n">
         <v>6</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -45417,9 +45144,6 @@
       <c r="O240" t="n">
         <v>6</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -45961,9 +45685,6 @@
       <c r="O243" t="n">
         <v>3</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -46357,9 +46078,6 @@
       <c r="O245" t="n">
         <v>13</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -46901,9 +46619,6 @@
       <c r="O248" t="n">
         <v>6</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -47297,9 +47012,6 @@
       <c r="O250" t="n">
         <v>11</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -47989,9 +47701,6 @@
       <c r="O254" t="n">
         <v>2</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -48615,9 +48324,6 @@
       <c r="O257" t="n">
         <v>8</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.17422579772276</v>
       </c>
@@ -49307,9 +49013,6 @@
       <c r="O261" t="n">
         <v>2</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -49703,9 +49406,6 @@
       <c r="O263" t="n">
         <v>12</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.2613386965841399</v>
       </c>
@@ -50395,9 +50095,6 @@
       <c r="O267" t="n">
         <v>3</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -50791,9 +50488,6 @@
       <c r="O269" t="n">
         <v>6</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -51483,9 +51177,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -51879,9 +51570,6 @@
       <c r="O275" t="n">
         <v>4</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -52571,9 +52259,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -52967,9 +52652,6 @@
       <c r="O281" t="n">
         <v>4</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -53511,9 +53193,6 @@
       <c r="O284" t="n">
         <v>2</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -53907,9 +53586,6 @@
       <c r="O286" t="n">
         <v>6</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -54599,9 +54275,6 @@
       <c r="O290" t="n">
         <v>2</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -54995,9 +54668,6 @@
       <c r="O292" t="n">
         <v>7</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -55539,9 +55209,6 @@
       <c r="O295" t="n">
         <v>5</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -55935,9 +55602,6 @@
       <c r="O297" t="n">
         <v>5</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.108891123576725</v>
       </c>
@@ -56627,9 +56291,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -57023,9 +56684,6 @@
       <c r="O303" t="n">
         <v>4</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.08711289886137998</v>
       </c>
@@ -57567,9 +57225,6 @@
       <c r="O306" t="n">
         <v>4</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -57963,9 +57618,6 @@
       <c r="O308" t="n">
         <v>6</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.1306693482920699</v>
       </c>
@@ -58507,9 +58159,6 @@
       <c r="O311" t="n">
         <v>3</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -58903,9 +58552,6 @@
       <c r="O313" t="n">
         <v>8</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.17422579772276</v>
       </c>
@@ -59447,9 +59093,6 @@
       <c r="O316" t="n">
         <v>1</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -59842,9 +59485,6 @@
       </c>
       <c r="O318" t="n">
         <v>9</v>
-      </c>
-      <c r="Q318" t="n">
-        <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>0.1960040224381049</v>
